--- a/modules/log/Dias.xlsx
+++ b/modules/log/Dias.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -795,9 +795,185 @@
         <v>52</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Dias</v>
+      </c>
+      <c r="B10" t="str">
+        <v>25230</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Бегенов Аваз</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Аликулова</v>
+      </c>
+      <c r="E10" t="str">
+        <v>16а</v>
+      </c>
+      <c r="F10" t="str">
+        <v>78189</v>
+      </c>
+      <c r="G10" t="str">
+        <v>160</v>
+      </c>
+      <c r="H10" t="str">
+        <v>518</v>
+      </c>
+      <c r="I10" t="str">
+        <v>358</v>
+      </c>
+      <c r="J10" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K10" t="str">
+        <v>12</v>
+      </c>
+      <c r="L10" t="str">
+        <v>5</v>
+      </c>
+      <c r="M10" t="str">
+        <v>14</v>
+      </c>
+      <c r="N10" t="str">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Dias</v>
+      </c>
+      <c r="B11" t="str">
+        <v>26806</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Сайдахметов Файзулла</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Алматинская</v>
+      </c>
+      <c r="E11" t="str">
+        <v>94</v>
+      </c>
+      <c r="F11" t="str">
+        <v>70850</v>
+      </c>
+      <c r="G11" t="str">
+        <v>490</v>
+      </c>
+      <c r="H11" t="str">
+        <v>605</v>
+      </c>
+      <c r="I11" t="str">
+        <v>115</v>
+      </c>
+      <c r="J11" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K11" t="str">
+        <v>12</v>
+      </c>
+      <c r="L11" t="str">
+        <v>9</v>
+      </c>
+      <c r="M11" t="str">
+        <v>10</v>
+      </c>
+      <c r="N11" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Dias</v>
+      </c>
+      <c r="B12" t="str">
+        <v>19500</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Бегметов Юлдаш</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Сайрамская</v>
+      </c>
+      <c r="E12" t="str">
+        <v>19ю</v>
+      </c>
+      <c r="F12" t="str">
+        <v>65990</v>
+      </c>
+      <c r="G12" t="str">
+        <v>882</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1045</v>
+      </c>
+      <c r="I12" t="str">
+        <v>163</v>
+      </c>
+      <c r="J12" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K12" t="str">
+        <v>12</v>
+      </c>
+      <c r="L12" t="str">
+        <v>17</v>
+      </c>
+      <c r="M12" t="str">
+        <v>19</v>
+      </c>
+      <c r="N12" t="str">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Dias</v>
+      </c>
+      <c r="B13" t="str">
+        <v>40829</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Беганова Нигора</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Сайрамская туп 4</v>
+      </c>
+      <c r="E13" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F13" t="str">
+        <v>83897</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>32</v>
+      </c>
+      <c r="I13" t="str">
+        <v>31</v>
+      </c>
+      <c r="J13" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K13" t="str">
+        <v>12</v>
+      </c>
+      <c r="L13" t="str">
+        <v>23</v>
+      </c>
+      <c r="M13" t="str">
+        <v>11</v>
+      </c>
+      <c r="N13" t="str">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N13"/>
   </ignoredErrors>
 </worksheet>
 </file>